--- a/img/BQ-Output.xlsx
+++ b/img/BQ-Output.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YWYD5I\Documents\Content-Production-for-Presentations\Slides_Meetings_Confs\DT-Production-cvscjo\img\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4946317E-1D8E-46B5-A6B6-34837D156D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F4077E-BE50-4952-8664-C512396B7173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{1E36B89C-9A83-488C-86CA-403B2B3FA45F}"/>
   </bookViews>
@@ -51,57 +51,30 @@
     <t>residuals.skewness:3</t>
   </si>
   <si>
-    <t>mod$result$preprocessing$diagnostics$skewness</t>
-  </si>
-  <si>
     <t>residuals.lb2:3</t>
   </si>
   <si>
-    <t>mod$result$preprocessing$diagnostics$lb2</t>
-  </si>
-  <si>
     <t>residuals.doornikhansen:3</t>
   </si>
   <si>
-    <t>mod$result$preprocessing$diagnostics$doornikhansen</t>
-  </si>
-  <si>
     <t>diagnostics.seas-sa-qs:2</t>
   </si>
   <si>
-    <t>mod$result$diagnostics$seas.qstest.sa</t>
-  </si>
-  <si>
     <t>diagnostics.seas-i-qs:2</t>
   </si>
   <si>
-    <t>mod$result$diagnostics$seas.qstest.i</t>
-  </si>
-  <si>
     <t>diagnostics.seas-sa-f:2</t>
   </si>
   <si>
-    <t>mod$result$diagnostics$seas.ftest.sa</t>
-  </si>
-  <si>
     <t>diagnostics.seas-i-f:2</t>
   </si>
   <si>
-    <t>mod$result$diagnostics$seas.ftest.i</t>
-  </si>
-  <si>
     <t>diagnostics.td-sa-last:2</t>
   </si>
   <si>
-    <t>mod$result$diagnostics$td.ftest.sa</t>
-  </si>
-  <si>
     <t>diagnostics.td-i-last:2</t>
   </si>
   <si>
-    <t>mod$result$diagnostics$td.ftest.i</t>
-  </si>
-  <si>
     <t>diagnostics.fcast-outsample-mean:2</t>
   </si>
   <si>
@@ -111,15 +84,9 @@
     <t>m-statistics.q-m2</t>
   </si>
   <si>
-    <t>mod$result$mstats$qm2</t>
-  </si>
-  <si>
     <t>m-statistics.m7</t>
   </si>
   <si>
-    <t>mod$result$mstats$m7</t>
-  </si>
-  <si>
     <t>Nom de variable dans le fichier demetra_m.csv (Cruncher ou GUI)</t>
   </si>
   <si>
@@ -132,85 +99,118 @@
     <t>Skewness test on Reg-Arima residuals</t>
   </si>
   <si>
+    <t>QS-Test de saisonnalité résiduelle sur la série cvs (sa) finale</t>
+  </si>
+  <si>
+    <t>QS- Test de saisonnalité résiduelle sur l'irrégulier (i) final</t>
+  </si>
+  <si>
+    <t>Ljung-Box test on Reg-Arima residuals</t>
+  </si>
+  <si>
+    <t>F-Test de saisonnalité résiduelle sur la série cvs (sa) finale</t>
+  </si>
+  <si>
+    <t>F-Test de saisonnalité résiduelle sur l'irrégulier (i) final</t>
+  </si>
+  <si>
+    <t>F-Test d'effets de jours ouvrables résiduels sur la série cvs (sa) finale</t>
+  </si>
+  <si>
+    <t>F-Test d'effets de jours ouvrables résiduels sur l'irrégulier (i) final</t>
+  </si>
+  <si>
+    <t>QS-Test  for residual seasonality on final irregular</t>
+  </si>
+  <si>
+    <t>F-Test  for residual seasonality on final irregular</t>
+  </si>
+  <si>
+    <t>QS-Test  for residual seasonality on final sa series</t>
+  </si>
+  <si>
+    <t>F-Test  for residual seasonality on final sa series</t>
+  </si>
+  <si>
+    <t>F-Test  for residual trading days effect on final sa series</t>
+  </si>
+  <si>
+    <t>F-Test  for residual trading days effect on final irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean equality test in and out of sample </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variance equality test in and out of sample </t>
+  </si>
+  <si>
+    <t>Décomposition X-11 : statistique Q-M2</t>
+  </si>
+  <si>
+    <t>Décomposition X-11 : statistique M7</t>
+  </si>
+  <si>
+    <t>Access with rjd3x13</t>
+  </si>
+  <si>
+    <t>X-11 decomposition: Q-M2 statistic</t>
+  </si>
+  <si>
+    <t>X-11 decomposition: M7 statistic</t>
+  </si>
+  <si>
+    <t>Normality (Doornik-Hansen) test on Reg-Arima residuals</t>
+  </si>
+  <si>
+    <t>Variable name in demetra_m.csv file (Cruncher or GUI)</t>
+  </si>
+  <si>
+    <t>m_sa$user_defined$`diagnostics.fcast-outsample-mean`</t>
+  </si>
+  <si>
+    <t>m_sa$user_defined$`diagnostics.fcast-outsample-variance`</t>
+  </si>
+  <si>
+    <t>m_sa$result$preprocessing$diagnostics$skewness</t>
+  </si>
+  <si>
+    <t>m_sa$result$preprocessing$diagnostics$lb2</t>
+  </si>
+  <si>
+    <t>m_sa$result$preprocessing$diagnostics$doornikhansen</t>
+  </si>
+  <si>
+    <t>m_sa$result$diagnostics$seas.qstest.sa</t>
+  </si>
+  <si>
+    <t>m_sa$result$diagnostics$seas.qstest.i</t>
+  </si>
+  <si>
+    <t>m_sa$result$diagnostics$seas.ftest.sa</t>
+  </si>
+  <si>
+    <t>m_sa$result$diagnostics$seas.ftest.i</t>
+  </si>
+  <si>
+    <t>m_sa$result$diagnostics$td.ftest.sa</t>
+  </si>
+  <si>
+    <t>m_sa$result$diagnostics$td.ftest.i</t>
+  </si>
+  <si>
+    <t>m_sa$result$mstats$qm2</t>
+  </si>
+  <si>
+    <t>m_sa$result$mstats$m7</t>
+  </si>
+  <si>
+    <t>Test de normalité (Doornik-Hansen) sur les résidus du modèle Reg-Arima</t>
+  </si>
+  <si>
     <t>Test de skewness sur les résidus du modèle Reg-Arima</t>
   </si>
   <si>
     <t>Test de Ljung-Box sur les résidus du modèle Reg-Arima</t>
-  </si>
-  <si>
-    <t>QS-Test de saisonnalité résiduelle sur la série cvs (sa) finale</t>
-  </si>
-  <si>
-    <t>QS- Test de saisonnalité résiduelle sur l'irrégulier (i) final</t>
-  </si>
-  <si>
-    <t>Test de normalité (Doornik-Hansen) sur les résidus du modèle Reg-Arima</t>
-  </si>
-  <si>
-    <t>Ljung-Box test on Reg-Arima residuals</t>
-  </si>
-  <si>
-    <t>F-Test de saisonnalité résiduelle sur la série cvs (sa) finale</t>
-  </si>
-  <si>
-    <t>F-Test de saisonnalité résiduelle sur l'irrégulier (i) final</t>
-  </si>
-  <si>
-    <t>F-Test d'effets de jours ouvrables résiduels sur la série cvs (sa) finale</t>
-  </si>
-  <si>
-    <t>F-Test d'effets de jours ouvrables résiduels sur l'irrégulier (i) final</t>
-  </si>
-  <si>
-    <t>QS-Test  for residual seasonality on final irregular</t>
-  </si>
-  <si>
-    <t>F-Test  for residual seasonality on final irregular</t>
-  </si>
-  <si>
-    <t>QS-Test  for residual seasonality on final sa series</t>
-  </si>
-  <si>
-    <t>F-Test  for residual seasonality on final sa series</t>
-  </si>
-  <si>
-    <t>F-Test  for residual trading days effect on final sa series</t>
-  </si>
-  <si>
-    <t>F-Test  for residual trading days effect on final irregular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean equality test in and out of sample </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variance equality test in and out of sample </t>
-  </si>
-  <si>
-    <t>Décomposition X-11 : statistique Q-M2</t>
-  </si>
-  <si>
-    <t>Décomposition X-11 : statistique M7</t>
-  </si>
-  <si>
-    <t>Access with rjd3x13</t>
-  </si>
-  <si>
-    <t>X-11 decomposition: Q-M2 statistic</t>
-  </si>
-  <si>
-    <t>X-11 decomposition: M7 statistic</t>
-  </si>
-  <si>
-    <t>Normality (Doornik-Hansen) test on Reg-Arima residuals</t>
-  </si>
-  <si>
-    <t>upcoming</t>
-  </si>
-  <si>
-    <t>à venir</t>
-  </si>
-  <si>
-    <t>Variable name in demetra_m.csv file (Cruncher or GUI)</t>
   </si>
 </sst>
 </file>
@@ -768,9 +768,9 @@
   <dimension ref="B2:J16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="52.08203125" customWidth="1"/>
-    <col min="3" max="3" width="30.5" customWidth="1"/>
-    <col min="4" max="4" width="41" customWidth="1"/>
+    <col min="2" max="2" width="60.25" customWidth="1"/>
+    <col min="3" max="3" width="31.75" customWidth="1"/>
+    <col min="4" max="4" width="47.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="14.5" thickBot="1"/>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>1</v>
@@ -787,146 +787,146 @@
     </row>
     <row r="4" spans="2:10" ht="21.75" customHeight="1">
       <c r="B4" s="4" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="21.75" customHeight="1">
       <c r="B5" s="4" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="21.75" customHeight="1">
       <c r="B6" s="4" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="21.75" customHeight="1">
       <c r="B7" s="4" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="21.75" customHeight="1">
       <c r="B8" s="4" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="21.75" customHeight="1">
       <c r="B9" s="4" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="21.75" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="21.75" customHeight="1">
       <c r="B11" s="4" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="21.75" customHeight="1">
       <c r="B12" s="4" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="21.75" customHeight="1">
       <c r="B13" s="4" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" ht="21.75" customHeight="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="34.5" customHeight="1">
       <c r="B14" s="4" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="21.75" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="J15" s="10"/>
     </row>
     <row r="16" spans="2:10" ht="21.75" customHeight="1" thickBot="1">
       <c r="B16" s="7" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -939,9 +939,9 @@
   <dimension ref="B1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="41.9140625" customWidth="1"/>
+    <col min="2" max="2" width="41.83203125" customWidth="1"/>
     <col min="3" max="3" width="30.08203125" customWidth="1"/>
-    <col min="4" max="4" width="41.83203125" customWidth="1"/>
+    <col min="4" max="5" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="14.5" thickBot="1"/>
@@ -950,153 +950,153 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="21.75" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="21.75" customHeight="1">
       <c r="B4" s="4" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="21.75" customHeight="1">
       <c r="B5" s="4" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="21.75" customHeight="1">
       <c r="B6" s="4" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="21.75" customHeight="1">
       <c r="B7" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="21.75" customHeight="1">
       <c r="B8" s="4" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="21.75" customHeight="1">
       <c r="B9" s="4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="21.75" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="21.75" customHeight="1">
       <c r="B11" s="4" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="21.75" customHeight="1">
       <c r="B12" s="4" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="21.75" customHeight="1">
       <c r="B13" s="4" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="21.75" customHeight="1">
       <c r="B14" s="4" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="21.75" customHeight="1" thickBot="1">
       <c r="B15" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
